--- a/reports/Debug-snowbowl-20260105/Month to Date (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260105/Month to Date (Prior Year)_Visits.xlsx
@@ -445,13 +445,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C3" s="2">
-        <v>529</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>1426</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -473,10 +473,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C5" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,10 +490,10 @@
         <v>45658</v>
       </c>
       <c r="C6" s="2">
-        <v>322</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,10 +501,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C7" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -515,13 +515,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C8" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C9" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C10" s="2">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C11" s="2">
-        <v>1102</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C12" s="2">
-        <v>236</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C13" s="2">
-        <v>902</v>
+        <v>1102</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C14" s="2">
-        <v>1268</v>
+        <v>236</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>902</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C16" s="2">
-        <v>7</v>
+        <v>1268</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,10 +641,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C17" s="2">
-        <v>1426</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -655,13 +655,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C18" s="2">
-        <v>12</v>
+        <v>1304</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C20" s="2">
-        <v>1304</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,10 +700,10 @@
         <v>45659</v>
       </c>
       <c r="C21" s="2">
-        <v>7</v>
+        <v>509</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C22" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C23" s="2">
-        <v>509</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C24" s="2">
         <v>5</v>
@@ -756,10 +756,10 @@
         <v>45662</v>
       </c>
       <c r="C25" s="2">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +767,10 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C27" s="2">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C28" s="2">
-        <v>2</v>
+        <v>1510</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C29" s="2">
-        <v>346</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,10 +823,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C30" s="2">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,10 +837,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C31" s="2">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C32" s="2">
-        <v>1510</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,13 +865,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C33" s="2">
-        <v>196</v>
+        <v>862</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C34" s="2">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,10 +893,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C35" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -907,13 +907,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C36" s="2">
-        <v>2</v>
+        <v>529</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +921,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C37" s="2">
-        <v>862</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,13 +935,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C38" s="2">
-        <v>57</v>
+        <v>346</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
